--- a/光伏配储项目/电价数据/2026/天马站.xlsx
+++ b/光伏配储项目/电价数据/2026/天马站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.50989</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38554</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7410599999999999</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.5709099999999999</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5732699999999999</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.4977</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.49299</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43754</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45436</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43901</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42306</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41935</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40875</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39808</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39979</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.3849</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40198</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42307</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41253</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35452</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39148</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38492</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41693</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42063</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41389</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42388</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.4128500000000001</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44388</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35733</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33725</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.2784700000000001</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29508</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30688</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.28733</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.30472</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.11243</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.09167</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.09809</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.08319</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.10715</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.0428</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.08481999999999999</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.10103</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.10203</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.08303000000000001</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08946</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.07148</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.05147</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.00329</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.1479</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21474</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.24126</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.26194</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.20197</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.07390000000000001</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.00087</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.27344</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.13137</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.27362</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.2634</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.30426</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.2661</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.1791</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.27865</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.51813</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.3746</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.46412</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.8271799999999999</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39264</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.58013</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.42981</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44015</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.41779</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.5641</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.43952</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.58921</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.79171</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.63422</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.6037100000000001</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.71097</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.78137</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.4159</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.6546799999999999</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.6053200000000001</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.6366799999999999</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.5834199999999999</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.57492</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.63062</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.6004299999999999</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.46488</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48567</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41599</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42563</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.68287</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.62655</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.76007</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.15851</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.81874</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.52573</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51958</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50544</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50739</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.49103</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39997</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47061</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37856</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38025</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39152</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37055</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35599</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.3591</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37547</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37538</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38031</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41985</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.50241</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.59836</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.68057</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.43097</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.36438</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.40902</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34763</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33538</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.40401</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50095</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.14728</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29941</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.03676</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.33189</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.31245</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.33394</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.34967</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.46978</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.75673</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.88176</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.31696</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.3489</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.36085</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.36329</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.35744</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.74026</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.47793</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.10188</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28174</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.30479</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.35936</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.31727</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.31431</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.45961</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.25962</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.24408</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.25587</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.45329</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.41059</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.29217</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.37506</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.5282100000000001</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.50242</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.68508</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.74914</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.75652</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.5016700000000001</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.48576</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.80633</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.48464</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.39755</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.88015</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.35557</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.45002</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.5926900000000001</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43994</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43358</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41234</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3368</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37841</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35635</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33453</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32149</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.52564</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.36956</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48023</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37838</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38177</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40219</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.3941</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39012</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38589</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36523</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43354</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44974</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39604</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36918</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37059</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35565</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.3611</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.3514</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36654</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35882</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38435</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47389</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44963</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44395</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39798</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35299</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36926</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34865</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.3514</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.31421</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.30787</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.31966</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.19167</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.35293</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.26574</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.31634</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.3177</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.29745</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34239</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.46272</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.39427</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.49814</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.3117200000000001</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.46955</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.38357</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.29247</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.14279</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.29365</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.24555</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.29447</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.27691</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.27605</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29341</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33888</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.3003</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.28185</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.37589</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.40479</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.39451</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.44017</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.39101</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.42812</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.35889</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.37355</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.50059</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.58756</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.49084</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.5880700000000001</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.32693</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.44062</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.40621</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.45449</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.39177</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.43181</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.42762</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.44807</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.43428</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.38145</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.36427</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.38686</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.38965</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39234</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36054</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34922</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34256</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.40156</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.32052</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.36533</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.36412</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.34436</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.35445</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.33339</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.32902</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46023</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.33377</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.32818</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.33479</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.31131</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.3136</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.30719</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35498</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38951</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.33643</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.34813</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.36704</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.36444</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.30507</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26834</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.29868</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.13991</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.20014</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.15163</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.25184</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.21132</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30145</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.50545</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.30502</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.40719</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.30686</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.05545000000000001</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.0513</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.11263</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.29499</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.28574</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.15109</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.16105</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.4896</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.05051</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.11719</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.23179</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.38952</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.35108</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.31149</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.22971</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.24682</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.21746</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.27516</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.14757</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.26868</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.2814</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.30332</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.33873</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.32654</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.3662</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.41756</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.5548500000000001</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.45261</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.44297</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.36713</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.35293</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.36935</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.3253</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.33551</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.30766</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31454</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32374</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29488</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31082</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.29731</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29673</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.29861</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.3708</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38268</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33903</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30132</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31118</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.30921</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.3093399999999999</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30757</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.29398</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30589</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.3087</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.29417</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.29854</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29026</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29026</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29033</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29807</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29221</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.2952</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31236</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32448</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33275</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32614</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27948</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26072</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.04561</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04651</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.04565</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.04608</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04413</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04822</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.04849000000000001</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04851</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.03551</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04758</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04492</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04203</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04018</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04057</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04147</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04106</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.0391</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04249</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04589</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04172</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04203</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04306</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04347</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04684000000000001</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04201</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04564</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21924</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04843</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.05418</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05575</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.00034</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.15197</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.04371</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.1037</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29003</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29275</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29367</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31517</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33487</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38508</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39167</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38698</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.38631</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34135</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.41007</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.3996</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.4271</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46765</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35457</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39654</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40017</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41742</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35524</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35114</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.66908</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40041</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44683</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42389</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42399</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35828</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33371</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30951</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32476</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35571</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34777</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34647</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31558</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32281</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30024</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32289</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34296</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.1025</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04681</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04568</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04599</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04599</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04599</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04532</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04363</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.03284</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04226</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10609</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.00041</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.03878</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.04736</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04306</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04349</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.0435</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04542</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04528</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04328</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04289</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04513</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04289</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04126</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04513</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04495</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04511</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04317</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04389</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04074000000000001</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04276</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04445</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04996</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04722999999999999</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04754</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20032</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14313</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29054</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29526</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30513</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30041</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29549</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29399</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29297</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29744</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29129</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29545</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.2693</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29433</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29853</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30887</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30439</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30238</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34814</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.3450299999999999</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36703</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36551</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33595</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31837</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40517</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32114</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.3078</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30184</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.2816</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29508</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29126</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28851</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.2814</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27161</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27142</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28148</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17271</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15896</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17134</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14804</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15977</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15896</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23674</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21438</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22692</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26944</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28621</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29121</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29126</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.2814</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28149</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28098</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.2707</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28135</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32296</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30549</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31684</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30973</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35936</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.3161</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29347</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38264</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42711</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45264</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33174</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41705</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41385</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38924</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40127</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30097</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29921</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15671</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.2925</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.3106</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31309</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31166</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30064</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38509</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50764</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62201</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49794</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78099</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92032</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.4945</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91723</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8724700000000001</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.3013</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.36301</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.89678</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63318</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.19621</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87325</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.54975</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.3402</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03933</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5401699999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79895</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53087</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.78099</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78389</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87776</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87805</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.50063</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.40598</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.40955</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.45851</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21666</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87917</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55123</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.63142</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54073</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.5004700000000001</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45702</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42541</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43886</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45043</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39062</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45284</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42039</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35317</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40011</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36535</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.3876</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41495</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43399</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39054</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.34692</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.3409700000000001</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40542</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.35234</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45092</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.4004</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58735</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42823</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5962999999999999</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60239</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6687799999999999</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.4657</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41673</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5777899999999999</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45054</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8763500000000001</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.63454</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8547899999999999</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.8366699999999999</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.86025</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44005</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33175</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30516</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.44589</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29716</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.28224</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31024</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35742</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33276</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33731</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33793</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30625</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31913</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34416</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31496</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30643</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.30275</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3122200000000001</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31382</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31226</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31556</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.3102</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31562</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32264</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32519</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35475</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34116</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34033</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33843</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33755</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41044</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.4131</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45295</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41546</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39189</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37535</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35352</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32875</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.93404</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36072</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.47046</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.38007</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.43955</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.49875</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38598</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.4102</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.37389</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.38654</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38914</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.3459</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32308</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40055</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.5007699999999999</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35735</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38802</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34371</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35108</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3555</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37094</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36323</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31661</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31368</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33275</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33687</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31508</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31058</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29068</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30487</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28956</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.28506</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16497</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.29934</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30797</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.32349</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30326</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29719</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26192</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19944</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27731</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.20743</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31647</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27728</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31156</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.3128</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35339</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31486</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31131</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31943</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31285</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29049</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30798</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31327</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29002</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34785</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25561</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32217</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.34207</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27625</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.3239</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38584</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43624</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.31283</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42324</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35145</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44862</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42078</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35909</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40083</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59789</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8904099999999999</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.31964</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.12661</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.6931</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.78134</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6446900000000001</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5767599999999999</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.44813</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.44752</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.4963</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43709</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43492</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41279</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41071</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42126</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.49689</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.4107</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43139</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41124</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43098</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38869</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42586</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.44781</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39447</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42104</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43182</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.4107</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41068</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.39862</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42148</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.38218</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.39968</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49932</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36205</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34612</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29666</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.3654</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30869</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30593</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.32249</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30372</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.02512</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.5618300000000001</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.37059</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.31776</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25009</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.55114</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.28597</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.29605</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.28801</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.16347</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.39615</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30258</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26263</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25686</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30519</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.27977</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28632</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29322</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.3162</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31042</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.32943</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31489</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.39867</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.39849</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35934</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33599</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.3704</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.36998</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36238</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.37504</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36302</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.57624</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46088</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.75983</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46186</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43783</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37554</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42339</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38631</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36928</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33413</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34079</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32922</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32452</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42142</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34388</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33535</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32617</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32623</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32492</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30992</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32592</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30995</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.3109</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.38997</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39888</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37424</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34891</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35393</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33149</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.28051</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33266</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.31754</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.2851</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.30225</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.28799</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23314</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14793</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.15207</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28848</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.1595</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14665</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.14409</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14649</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.14464</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.26514</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.14874</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.27411</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.26393</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.14705</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.12573</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.11572</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.10791</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.14251</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.14306</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14772</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28393</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.32096</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.32874</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.30903</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.33911</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.3657</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34141</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37829</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34593</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39655</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38366</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44767</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.3988</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39001</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40062</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39647</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44243</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43768</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43701</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44183</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44161</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40096</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.3892</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39644</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3904</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35941</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34806</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34924</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5356799999999999</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38727</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46522</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42127</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.4135</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.36918</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.37889</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.37837</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39114</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37818</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36867</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37894</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35916</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.38958</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36912</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.37899</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34657</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35459</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35477</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36915</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.37891</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.33975</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32829</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34878</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.36524</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29576</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31556</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30663</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28963</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28124</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.26665</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26202</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.19551</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30451</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.24724</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.23907</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26613</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29826</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28475</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30292</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.2985</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.31519</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31365</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29116</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28067</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.23867</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.3122200000000001</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30161</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30139</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28189</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.3161600000000001</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33313</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32493</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.32592</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35065</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34563</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.39177</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.38535</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.39853</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.25563</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.35498</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.3804</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35525</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35478</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41805</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.35309</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.3667</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37327</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.37962</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.37973</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38445</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35111</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35968</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36955</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.43482</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37041</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39855</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38543</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36265</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34186</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34737</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.35285</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34035</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34275</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33812</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34502</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34619</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36413</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31355</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32613</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32195</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33507</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.29771</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.38904</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.3573</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.30202</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.39982</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.44754</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.43918</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.30276</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.29192</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.36962</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>-0.00161</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.28413</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25043</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.2689</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.09545999999999999</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.21638</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.25352</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.29426</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.29394</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.27574</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.30043</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.31238</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.30893</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.29124</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.32026</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.41525</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.3414</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.34348</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35247</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.38625</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.31931</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.3264</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.3405899999999999</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.33607</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.44428</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.46031</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.71121</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36366</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.38959</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33564</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.32347</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.52191</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.27154</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.3849</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.3045</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.33137</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.33042</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.30534</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30947</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.30624</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.29002</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32468</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.35662</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33053</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32576</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.31986</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.3239</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32725</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32703</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32645</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32096</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32655</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33554</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.35243</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34114</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33811</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32151</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33436</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34312</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34825</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32072</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32448</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31739</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34085</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34432</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31203</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28396</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32564</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33009</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32633</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31902</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32048</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31425</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.3096</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.30386</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.32407</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33419</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36079</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33137</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.3792</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36418</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.37049</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36527</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37582</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36336</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39887</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38695</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37144</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40341</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35496</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38991</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.38085</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35074</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.35621</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34965</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35221</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35695</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.35488</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.35472</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36736</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.35192</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33721</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34359</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37719</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.34213</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34512</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.35474</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.35474</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.33071</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.35331</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33265</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30346</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32703</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33052</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32517</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31802</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36885</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32738</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31971</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31587</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32628</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32329</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33242</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33696</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34491</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35832</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.40578</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.36532</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35434</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36572</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35919</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38143</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37962</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38102</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38458</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.43779</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41002</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.39029</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37903</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6808999999999999</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.78255</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47487</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.33649</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.4572</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39225</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35574</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.36575</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.34361</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34913</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41658</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.3771600000000001</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37116</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36237</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35939</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.36465</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36053</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35923</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35311</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36055</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35888</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35221</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35952</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37074</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.3564</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.38818</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38184</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.3562</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35137</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.36348</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35427</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33239</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32664</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26511</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14639</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30111</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28531</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28399</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19883</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.25708</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27984</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31584</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27995</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.21828</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.26198</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28489</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27815</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28983</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.29123</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30516</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32178</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14996</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29302</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.29582</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32515</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.34094</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33566</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.33297</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.31255</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.35848</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31668</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.3585</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43333</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38374</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.42343</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.61422</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.65484</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.68037</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.48937</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.73733</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.52391</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.8817</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.46945</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.48242</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40793</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.38264</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.3623</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.4835</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43068</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.42969</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.38013</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37484</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36015</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34399</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49121</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.55447</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.4985</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.50038</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42183</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.40341</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40782</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41579</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40966</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41912</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39918</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39832</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41435</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40645</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39307</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38603</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41622</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38615</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41889</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38847</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40174</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.4017</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41421</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.4033</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.4471</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45568</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.5612699999999999</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.49582</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.44727</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.56564</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.46266</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.4418</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.3548</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38799</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.38944</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.42433</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.42522</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.51838</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.45327</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.36493</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.37858</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.38472</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.4021</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.28794</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.32189</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.32992</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.36431</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.64049</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.36489</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.15699</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.28063</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.32719</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.31167</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.34643</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37187</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.3701</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.35771</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35278</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.38132</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33742</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.40996</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.43325</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.48806</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43524</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.50941</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.53825</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.60533</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.7756000000000001</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.79247</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.9315099999999999</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.71126</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.80341</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.5984400000000001</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.55137</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.9177999999999999</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.8420299999999999</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6293300000000001</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.7027</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.45148</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47144</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.50429</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47831</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.49121</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41835</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5642</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42881</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44349</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.46761</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.45266</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.43194</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.45556</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.43061</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40017</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.46851</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39838</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40712</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.40785</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38709</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.3787</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37375</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35687</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37673</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37123</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36321</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.39452</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39028</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.38635</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.37096</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36501</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35768</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.38636</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.40663</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36965</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.39387</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39698</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.4034</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.3932</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.3691</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34477</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33776</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34604</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.37543</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.18174</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.37919</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.33322</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.3472</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.35778</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40541</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.3577</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.44848</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.39091</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.4644</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31319</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.11069</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18102</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30051</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29517</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32036</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35293</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34874</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35059</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.37215</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.37842</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37305</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.3883</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41574</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36928</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.42746</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41233</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41165</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38176</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.37535</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38461</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39029</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40894</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.4082</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34555</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.37224</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37686</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.4081</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.38634</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35507</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.40155</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38049</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37509</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36362</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39552</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.38061</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36562</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44499</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36053</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39302</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39286</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35647</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37907</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37875</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35778</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.3555</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35934</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34647</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35122</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.34021</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.34003</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34035</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34544</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33045</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33186</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33876</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31113</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30578</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.27071</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32103</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31582</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.31026</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22843</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28871</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.2307</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.28876</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25048</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.25321</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13969</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29255</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29959</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.31357</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.24991</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04335</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25169</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28755</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.16903</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18084</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.27263</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30941</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30914</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.22775</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.24814</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26163</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23174</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27523</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28431</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28257</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32647</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.3071</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.3529</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34807</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35208</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.3536</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.35694</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.3728399999999999</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35687</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35794</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.37953</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36906</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36965</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.36977</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36436</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37926</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36413</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36914</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36049</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34888</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.3486</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35069</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34341</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33034</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31901</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30926</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.3092</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.3141</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31064</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.3098399999999999</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31244</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30926</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30659</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30615</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.3073</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31043</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31125</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29096</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.26323</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.25063</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.17166</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.21188</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.2093</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01782</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00027</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.0272</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04974</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.10877</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.01385</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03974</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04975</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.02224</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.0446</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04288</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04898</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.0487</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02696</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.03265999999999999</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04976</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.11736</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04975</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04976</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00274</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.28829</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.0498</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04976</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.03288</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04975</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04978</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04285</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.17094</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.20255</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.24046</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27951</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.26829</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.2699</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.26903</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.27386</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.28915</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.30872</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.29663</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.29658</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28351</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30927</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30584</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.31073</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29656</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.30861</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.29395</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.30868</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.3006</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.32857</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.40978</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.32769</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.31374</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.29616</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.29666</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.28928</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.28851</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29551</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.15604</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.59372</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.36133</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.18313</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.34675</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.30186</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.29986</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.27622</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.30833</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.3117200000000001</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.29169</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.2825299999999999</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.25854</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.24944</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.27472</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.26397</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.23335</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.26083</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.2553</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.28572</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.27815</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.28269</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.26086</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.30552</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.28427</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.31913</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.31568</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.28482</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.28495</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.23931</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.18033</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.65728</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.66146</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.6726599999999999</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.59465</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.17374</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.09303</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.24288</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.1873</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.1372</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.14321</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.10145</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.23196</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.12599</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.3167</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.04999</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.06491</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.1155</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.18437</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.02436</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.13541</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.1404</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.15969</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.01127</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.11883</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.12447</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.1258</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.15581</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25357</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29232</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.27363</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.31365</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32343</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33464</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33155</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33373</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35293</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.35826</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.3792</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.37607</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.39373</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37079</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.36991</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.35972</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.35967</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35179</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36925</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35258</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36265</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.3742</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.33287</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32875</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32974</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.3405899999999999</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32385</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35589</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.37169</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.34414</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33821</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33174</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33155</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34903</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34082</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32809</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.07562999999999999</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.3338</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32694</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.34089</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33245</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33735</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.34613</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.47938</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.54823</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.37432</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.4146</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32362</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.29133</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.31554</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.41133</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.42095</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.46071</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.38467</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.45812</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.38295</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.37295</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.43959</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.32572</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32597</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.3113</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.13937</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27408</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27006</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30509</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32691</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32561</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.33196</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.27692</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.30474</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31107</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29143</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31221</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31796</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32213</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32705</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.3464100000000001</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34493</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35319</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33447</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35733</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.35582</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34966</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36196</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37668</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.44486</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35767</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.41687</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.37536</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.36563</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35536</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36762</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35729</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32145</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33324</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33317</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37505</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.3314</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.28727</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31659</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.34243</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34512</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31368</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35211</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33617</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32065</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33014</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34645</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32325</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.37548</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35775</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35189</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.38318</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.61226</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.32228</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.5866699999999999</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.35341</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.5297000000000001</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.37277</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36768</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35336</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.3045</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.34611</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33822</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.39361</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.34968</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.30772</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26058</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34681</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34926</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.28144</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.2832</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.3346</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.33379</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33865</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.36157</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.41471</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39827</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.5054999999999999</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.51915</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.45327</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.4649</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.41231</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.44548</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.38409</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.40907</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.4303</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.39015</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.37373</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.38987</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.38846</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.37369</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.39058</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41757</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.46262</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.40321</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.38376</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.48023</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.41328</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38896</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.41327</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.37944</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>1.79331</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3727</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.51778</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.37511</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.47818</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.38316</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.3832</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.36732</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38074</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37536</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37419</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37863</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37705</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36902</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36681</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35553</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36335</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37609</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.40945</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.38158</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36975</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35469</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.38737</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.40357</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.37007</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.37179</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43132</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37743</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.37532</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.29134</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35356</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31744</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36524</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.26499</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.37773</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35422</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.35884</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.30929</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.32764</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33395</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.30717</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.31413</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33358</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.33836</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33656</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.30432</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34616</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.38079</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.3727</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.38191</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.38829</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.46635</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.39535</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.44554</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.42726</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.42699</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5970700000000001</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.59488</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.39554</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.46178</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.5796699999999999</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.51286</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.56147</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.52563</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.40719</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.5689299999999999</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.51912</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.99203</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.87329</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.60434</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.59873</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.46069</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.40934</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.38055</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37772</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37313</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37958</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27039</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36972</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.3672</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33873</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33888</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34827</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33728</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34341</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.34064</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33733</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.3605</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33897</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.32225</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.32124</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.31506</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.35158</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.37112</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30727</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.30267</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.29679</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.3178</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.24381</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.27235</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.28492</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.12658</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.21388</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.17994</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.05597</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.28922</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.3083</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.13459</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.02438</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.19441</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.16281</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.00338</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.29531</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.25544</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.05207</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.04802</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.06148</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.14648</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.06945</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.16948</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.13824</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.16346</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.26189</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.29746</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.29948</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.28265</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.36491</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.34752</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.34841</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.36744</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36152</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.26108</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.3492</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.35609</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.30931</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.37978</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.3948</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.40882</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.3828</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.4143</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.41894</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38736</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39214</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.42449</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39417</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.39155</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.42563</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.38539</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.44596</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.39651</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.38889</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.52771</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.38059</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.3467</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.97072</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.36819</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.48256</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.43078</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.38038</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.34714</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.38687</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.37945</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38448</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.35746</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.36052</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.35267</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37789</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36463</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38094</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38668</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.36181</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36093</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.36441</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36656</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.36243</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36847</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38264</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34678</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33933</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.31364</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.31768</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33271</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.32643</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.31391</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.29869</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.2752</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.26885</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.28057</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.27002</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.11443</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.01808</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.01821</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.01736</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.03903</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.17435</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.03996</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.005889999999999999</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01816</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04562</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.0147</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.01348</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.01464</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.1618</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.26223</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.04435</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.24451</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.16042</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.25629</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.30562</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.28798</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.32661</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.30945</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.31336</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.32382</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.31662</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.35788</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.34332</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.48062</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.41639</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.40612</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36266</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37127</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.38915</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36512</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.3440299999999999</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.39303</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.58433</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38642</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37905</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39133</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.39604</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.37266</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.40238</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.35489</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.40011</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.42536</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.38537</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.39532</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.36821</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.37386</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.36725</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36323</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.37542</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.5982000000000001</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.38719</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.38916</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37165</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.36529</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.3681</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.35664</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.43942</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.35545</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39124</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.38015</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.35525</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.35404</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34877</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34721</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.35521</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.34183</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.28512</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.26262</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.23617</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.14719</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.21374</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.23733</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.24087</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.11704</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.15524</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.04697</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.03367</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04697</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04774</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.04657</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04682</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04447</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.04179</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.08083</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.02891</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.0649</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.09973</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.17625</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.20086</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.12384</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.2682</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.23575</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.1269</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.04846</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.2672</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.15138</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.11954</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.24058</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.19221</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.24866</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.25203</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.21011</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.25244</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.28382</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.28536</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.30837</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.31474</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.31854</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.37137</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.34967</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.34025</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38753</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37015</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37985</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.38695</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38824</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.40034</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.41275</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.5096000000000001</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.4015</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41125</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.41226</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.4045</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38225</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.39411</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40932</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38405</v>
       </c>
     </row>
   </sheetData>
